--- a/output/stock_quant_scores/KMI_balance_df.xlsx
+++ b/output/stock_quant_scores/KMI_balance_df.xlsx
@@ -1665,26 +1665,36 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>33210000000</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>-1992000000</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>30823000000</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-10595000000</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>38495000000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1692,7 +1702,9 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>5821000000</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1705,7 +1717,9 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>70416000000</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
@@ -1728,13 +1742,17 @@
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>3829000000</v>
+      </c>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="n">
         <v>185000000</v>
       </c>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>562000000</v>
+      </c>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="n">
@@ -1747,7 +1765,9 @@
       <c r="BV6" t="n">
         <v>0</v>
       </c>
-      <c r="BW6" t="inlineStr"/>
+      <c r="BW6" t="n">
+        <v>1140000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
